--- a/data/attendance/AMPHI_كحال_فرنسية_ادبي.xlsx
+++ b/data/attendance/AMPHI_كحال_فرنسية_ادبي.xlsx
@@ -143,7 +143,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
   <si>
-    <t>كحال فرنسية ادبي  |  AMPHI  |  BAC  |  ريم كحال</t>
+    <t>كحال فرنسية ادبي  |  AMPHI  |  BAC  |  كحال ريم</t>
   </si>
   <si>
     <t>class_id=14</t>

--- a/data/attendance/AMPHI_كحال_فرنسية_ادبي.xlsx
+++ b/data/attendance/AMPHI_كحال_فرنسية_ادبي.xlsx
@@ -20,119 +20,126 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>student_id:12e80561-aa12-447b-87de-f9fac78f8888</t>
+          <t>student_id:46a6adb3-93c6-412d-aaec-fc96a0919f31</t>
         </r>
       </text>
     </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <t>student_id:f492322c-de39-41e5-a7f1-f9906a8bd5ad</t>
+          <t>student_id:d133b1c1-28a3-4b97-a9db-6b476ae244b4</t>
         </r>
       </text>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <t>student_id:832482ef-6e09-47f9-a5bc-1f81bd04138e</t>
+          <t>student_id:6a75f326-77ad-4d47-9e88-ead02d7c4b58</t>
         </r>
       </text>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <t>student_id:cb154650-95ee-4dec-a601-1f898c42fb1d</t>
+          <t>student_id:706ecf15-8a21-4df2-9994-901d88ca9cdc</t>
         </r>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <t>student_id:d7ecc852-3b0f-4520-986c-d15db2a04963</t>
+          <t>student_id:4919300a-6f37-4a88-9414-45316707a25f</t>
         </r>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <t>student_id:07aa9cd5-b9be-4384-998f-3062fb953d3d</t>
+          <t>student_id:abbf565a-6277-46a7-9673-f053d01d6e24</t>
         </r>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <t>student_id:06c280e7-922d-4ab4-a3dd-aebbd06e82b4</t>
+          <t>student_id:0a76d7d3-5f1e-4dc0-bb7d-59b454c144fc</t>
         </r>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <t>student_id:12c63b78-6810-412b-9305-7c108d22cb2a</t>
+          <t>student_id:59b4f620-8e75-44c0-aadf-45cabeb9141e</t>
         </r>
       </text>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <t>student_id:fbb36c23-8313-4775-a454-7a41ba98d316</t>
+          <t>student_id:09d38764-9dd3-45fc-ab46-179050340c91</t>
         </r>
       </text>
     </comment>
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <t>student_id:295fb726-dc78-4501-8452-e1540e587518</t>
+          <t>student_id:e19083e5-fb52-4474-9b87-f7ac097a6fde</t>
         </r>
       </text>
     </comment>
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <t>student_id:4bab72ed-65ca-45b3-868f-8c300dd91fa2</t>
+          <t>student_id:1ef83844-49f4-4e07-9ba1-3a3d9c7f7fff</t>
         </r>
       </text>
     </comment>
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <t>student_id:74871226-903d-4009-894c-c5fd7618ce67</t>
+          <t>student_id:1070542a-17c7-4ca0-847b-5364957b8354</t>
         </r>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <t>student_id:0f019196-18d8-4b1f-b4cc-c5d08d654421</t>
+          <t>student_id:94d34ea3-c206-4873-af58-455c6ec4c4e5</t>
         </r>
       </text>
     </comment>
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <t>student_id:c2c983e6-937c-4481-95c3-efc31045def5</t>
+          <t>student_id:d0aeddb3-fae7-4860-a750-94ac3ae004f0</t>
         </r>
       </text>
     </comment>
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <t>student_id:1f7a458f-36fe-49c0-b760-4f3080d291db</t>
+          <t>student_id:c01f45e3-eec2-4c07-b9aa-1b000085c506</t>
         </r>
       </text>
     </comment>
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <t>student_id:5b6240a2-7fc4-4798-85d4-4b82fe9f0a2b</t>
+          <t>student_id:54dc6de3-ab5a-4546-a3fb-d4c433a46fb5</t>
         </r>
       </text>
     </comment>
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <t>student_id:29f6584c-8030-4885-a632-61bf5667c736</t>
+          <t>student_id:36a738f3-91c6-49c9-a1c4-e503f61941ab</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0">
+      <text>
+        <r>
+          <t>student_id:bdb88144-8c8b-448c-a78f-9d0b178bcf91</t>
         </r>
       </text>
     </comment>
@@ -141,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
   <si>
     <t>كحال فرنسية ادبي  |  AMPHI  |  BAC  |  كحال ريم</t>
   </si>
@@ -164,61 +171,61 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>05/09/2026</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
+    <t>دلوش ملاك</t>
+  </si>
+  <si>
     <t>مخلوفي ندير</t>
   </si>
   <si>
+    <t>بيدي وصال أسماء</t>
+  </si>
+  <si>
     <t>مالكي دارين</t>
   </si>
   <si>
+    <t>كريس امينة</t>
+  </si>
+  <si>
+    <t>حطاب ميسون</t>
+  </si>
+  <si>
+    <t>بودفة عبد الرحيم</t>
+  </si>
+  <si>
+    <t>ناصر سيرين</t>
+  </si>
+  <si>
+    <t>بن عويرة مقيم</t>
+  </si>
+  <si>
+    <t>داموس محمد</t>
+  </si>
+  <si>
+    <t>بغالي ريتاج</t>
+  </si>
+  <si>
+    <t>فيلالي ميليسا</t>
+  </si>
+  <si>
+    <t>عيساني رتاج</t>
+  </si>
+  <si>
+    <t>عشي انيا</t>
+  </si>
+  <si>
     <t>قروط علاء الدين</t>
   </si>
   <si>
-    <t>حطاب ميسون</t>
-  </si>
-  <si>
-    <t>ناصر سيرين</t>
-  </si>
-  <si>
-    <t>بيدي وصال أسماء</t>
-  </si>
-  <si>
-    <t>كريس امينة</t>
-  </si>
-  <si>
-    <t>بودفة عبد الرحيم</t>
-  </si>
-  <si>
-    <t>داموس محمد</t>
-  </si>
-  <si>
-    <t>بن عويرة مقيم</t>
-  </si>
-  <si>
-    <t>فيلالي ميليسا</t>
-  </si>
-  <si>
-    <t>عيساني رتاج</t>
-  </si>
-  <si>
-    <t>بغالي ريتاج</t>
-  </si>
-  <si>
-    <t>دلوش ملاك</t>
-  </si>
-  <si>
-    <t>عشي انيا</t>
-  </si>
-  <si>
     <t>بنوتة بهاء</t>
   </si>
   <si>
     <t>نايلي ميار</t>
+  </si>
+  <si>
+    <t>مريخي شهد</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -738,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -828,45 +835,45 @@
         <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>47</v>
+        <v>218</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -907,10 +914,10 @@
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -951,10 +958,10 @@
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -995,10 +1002,10 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>58</v>
+        <v>233</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -1039,10 +1046,10 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -1083,10 +1090,10 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1127,10 +1134,10 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>464</v>
+        <v>242</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1171,10 +1178,10 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>465</v>
+        <v>253</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -1215,10 +1222,10 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>471</v>
+        <v>254</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -1259,10 +1266,10 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>477</v>
+        <v>257</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
@@ -1303,10 +1310,10 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>498</v>
+        <v>259</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="8">
         <v>0</v>
@@ -1347,10 +1354,10 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>499</v>
+        <v>291</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="9">
         <v>0</v>
@@ -1391,10 +1398,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>500</v>
+        <v>292</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="8">
         <v>0</v>
@@ -1435,10 +1442,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>501</v>
+        <v>293</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="9">
         <v>0</v>
@@ -1479,10 +1486,10 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>502</v>
+        <v>294</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="8">
         <v>0</v>
@@ -1523,10 +1530,10 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>503</v>
+        <v>295</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="9">
         <v>0</v>
@@ -1567,45 +1574,89 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>504</v>
+        <v>296</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>297</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="8">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8">
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1638,7 +1689,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -1653,7 +1704,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -1683,7 +1734,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -1698,7 +1749,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/attendance/AMPHI_كحال_فرنسية_ادبي.xlsx
+++ b/data/attendance/AMPHI_كحال_فرنسية_ادبي.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:46a6adb3-93c6-412d-aaec-fc96a0919f31</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d133b1c1-28a3-4b97-a9db-6b476ae244b4</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6a75f326-77ad-4d47-9e88-ead02d7c4b58</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:706ecf15-8a21-4df2-9994-901d88ca9cdc</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4919300a-6f37-4a88-9414-45316707a25f</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:abbf565a-6277-46a7-9673-f053d01d6e24</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0a76d7d3-5f1e-4dc0-bb7d-59b454c144fc</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:59b4f620-8e75-44c0-aadf-45cabeb9141e</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:09d38764-9dd3-45fc-ab46-179050340c91</t>
         </r>
       </text>
@@ -149,13 +83,6 @@
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e19083e5-fb52-4474-9b87-f7ac097a6fde</t>
         </r>
       </text>
@@ -163,13 +90,6 @@
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1ef83844-49f4-4e07-9ba1-3a3d9c7f7fff</t>
         </r>
       </text>
@@ -177,97 +97,48 @@
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:1070542a-17c7-4ca0-847b-5364957b8354</t>
+          <t>student_id:29e02164-41d8-4b66-b25b-ca7ec7a151ff</t>
         </r>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:94d34ea3-c206-4873-af58-455c6ec4c4e5</t>
+          <t>student_id:1070542a-17c7-4ca0-847b-5364957b8354</t>
         </r>
       </text>
     </comment>
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:d0aeddb3-fae7-4860-a750-94ac3ae004f0</t>
+          <t>student_id:94d34ea3-c206-4873-af58-455c6ec4c4e5</t>
         </r>
       </text>
     </comment>
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:c01f45e3-eec2-4c07-b9aa-1b000085c506</t>
+          <t>student_id:d0aeddb3-fae7-4860-a750-94ac3ae004f0</t>
         </r>
       </text>
     </comment>
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:54dc6de3-ab5a-4546-a3fb-d4c433a46fb5</t>
+          <t>student_id:c01f45e3-eec2-4c07-b9aa-1b000085c506</t>
         </r>
       </text>
     </comment>
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:36a738f3-91c6-49c9-a1c4-e503f61941ab</t>
+          <t>student_id:54dc6de3-ab5a-4546-a3fb-d4c433a46fb5</t>
         </r>
       </text>
     </comment>
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:bdb88144-8c8b-448c-a78f-9d0b178bcf91</t>
         </r>
       </text>
@@ -277,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>كحال فرنسية ادبي  |  AMPHI  |  BAC  |  كحال ريم</t>
   </si>
@@ -291,6 +162,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -309,6 +183,9 @@
     <t>26/09/2026</t>
   </si>
   <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -345,10 +222,13 @@
     <t>بغالي ريتاج</t>
   </si>
   <si>
+    <t>نايلي ميار غفران</t>
+  </si>
+  <si>
     <t>فيلالي ميليسا</t>
   </si>
   <si>
-    <t>عيساني رتاج</t>
+    <t>عيساني رتاج خديجة</t>
   </si>
   <si>
     <t>عشي انيا</t>
@@ -360,9 +240,6 @@
     <t>بنوتة بهاء</t>
   </si>
   <si>
-    <t>نايلي ميار</t>
-  </si>
-  <si>
     <t>مريخي شهد</t>
   </si>
   <si>
@@ -393,7 +270,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -415,40 +295,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -535,7 +408,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -891,14 +764,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -916,7 +789,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -926,10 +799,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -971,63 +847,63 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>218</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="8">
         <v>0</v>
@@ -1057,21 +933,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>220</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
         <v>0</v>
@@ -1101,21 +977,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>226</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
       </c>
       <c r="D7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="8">
         <v>0</v>
@@ -1145,21 +1021,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>233</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -1189,21 +1065,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>240</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -1233,21 +1109,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>241</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -1277,21 +1153,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>242</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -1321,15 +1197,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>253</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -1365,12 +1241,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>254</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -1409,21 +1285,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>257</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
       </c>
       <c r="D14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -1453,21 +1329,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>259</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -1497,241 +1373,241 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
+        <v>264</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>291</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="9">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="B17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>292</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8">
-        <v>0</v>
-      </c>
-      <c r="N17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>293</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9">
-        <v>0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="9">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="B19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>294</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="8">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8">
-        <v>0</v>
-      </c>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="B20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
         <v>295</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="9">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9">
-        <v>1</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9">
-        <v>0</v>
-      </c>
-      <c r="G20" s="9">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9">
-        <v>0</v>
-      </c>
-      <c r="N20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>296</v>
-      </c>
       <c r="B21" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="8">
         <v>0</v>
       </c>
       <c r="D21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="8">
         <v>0</v>
@@ -1761,12 +1637,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>297</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22" s="9">
         <v>0</v>
@@ -1775,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
@@ -1811,7 +1687,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1821,89 +1697,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>